--- a/data/result_20260903_110042 (linkage info).xlsx
+++ b/data/result_20260903_110042 (linkage info).xlsx
@@ -5,19 +5,23 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:28001_{9E50861D-CCDC-4232-BF9A-C298C134C6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD22A26D-1ADC-4710-BCF2-8D3F16E18EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results export" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="unique_linked_id" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results export'!$A$1:$J$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$D$27</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="20">
   <si>
     <t>target_user_id</t>
   </si>
@@ -88,14 +92,20 @@
     <t>Permanently</t>
   </si>
   <si>
-    <t>UID</t>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>Fully Banned</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -104,36 +114,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -141,16 +137,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -582,10 +591,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>23938356</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>2725817</v>
       </c>
       <c r="C2" t="s">
@@ -614,10 +623,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>23938356</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>3560834</v>
       </c>
       <c r="C3" t="s">
@@ -646,10 +655,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>23938356</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>3728701</v>
       </c>
       <c r="C4" t="s">
@@ -678,10 +687,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>23938356</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>35433398</v>
       </c>
       <c r="C5" t="s">
@@ -710,10 +719,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>42459206</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>42458992</v>
       </c>
       <c r="C6" t="s">
@@ -742,10 +751,10 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>42459206</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>42458992</v>
       </c>
       <c r="C7" t="s">
@@ -774,10 +783,10 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>42459206</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>42459099</v>
       </c>
       <c r="C8" t="s">
@@ -806,10 +815,10 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>42459206</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>42459099</v>
       </c>
       <c r="C9" t="s">
@@ -838,10 +847,10 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>42459206</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
         <v>42459241</v>
       </c>
       <c r="C10" t="s">
@@ -870,10 +879,10 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>42459206</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
         <v>42459241</v>
       </c>
       <c r="C11" t="s">
@@ -902,10 +911,10 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>42459206</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12">
         <v>42459298</v>
       </c>
       <c r="C12" t="s">
@@ -934,10 +943,10 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>42459206</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13">
         <v>42459298</v>
       </c>
       <c r="C13" t="s">
@@ -966,10 +975,10 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>42598944</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14">
         <v>42011766</v>
       </c>
       <c r="C14" t="s">
@@ -998,10 +1007,10 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="A15">
         <v>42598944</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
         <v>42406507</v>
       </c>
       <c r="C15" t="s">
@@ -1030,10 +1039,10 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>42598944</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16">
         <v>42406507</v>
       </c>
       <c r="C16" t="s">
@@ -1062,10 +1071,10 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>42598944</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17">
         <v>42426592</v>
       </c>
       <c r="C17" t="s">
@@ -1094,10 +1103,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>42598944</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18">
         <v>42426641</v>
       </c>
       <c r="C18" t="s">
@@ -1126,10 +1135,10 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>42598944</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19">
         <v>42787717</v>
       </c>
       <c r="C19" t="s">
@@ -1158,10 +1167,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>42598944</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20">
         <v>42787717</v>
       </c>
       <c r="C20" t="s">
@@ -1190,10 +1199,10 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>42598944</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21">
         <v>43110281</v>
       </c>
       <c r="C21" t="s">
@@ -1222,10 +1231,10 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="A22">
         <v>42758642</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22">
         <v>42406507</v>
       </c>
       <c r="C22" t="s">
@@ -1254,10 +1263,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+      <c r="A23">
         <v>42758642</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23">
         <v>42705635</v>
       </c>
       <c r="C23" t="s">
@@ -1286,10 +1295,10 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="A24">
         <v>42758642</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24">
         <v>42731028</v>
       </c>
       <c r="C24" t="s">
@@ -1318,10 +1327,10 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="A25">
         <v>42758642</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25">
         <v>42731028</v>
       </c>
       <c r="C25" t="s">
@@ -1350,10 +1359,10 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="A26">
         <v>42758642</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26">
         <v>42787717</v>
       </c>
       <c r="C26" t="s">
@@ -1382,10 +1391,10 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="A27">
         <v>42758642</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27">
         <v>42787717</v>
       </c>
       <c r="C27" t="s">
@@ -1414,10 +1423,10 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+      <c r="A28">
         <v>42787717</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28">
         <v>42406507</v>
       </c>
       <c r="C28" t="s">
@@ -1446,10 +1455,10 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+      <c r="A29">
         <v>42787717</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29">
         <v>42406507</v>
       </c>
       <c r="C29" t="s">
@@ -1478,10 +1487,10 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+      <c r="A30">
         <v>42787717</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30">
         <v>42426592</v>
       </c>
       <c r="C30" t="s">
@@ -1510,10 +1519,10 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+      <c r="A31">
         <v>42787717</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31">
         <v>42731028</v>
       </c>
       <c r="C31" t="s">
@@ -1542,10 +1551,10 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="A32">
         <v>42787717</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32">
         <v>43110281</v>
       </c>
       <c r="C32" t="s">
@@ -1574,10 +1583,10 @@
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="A33">
         <v>42814075</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33">
         <v>42406507</v>
       </c>
       <c r="C33" t="s">
@@ -1606,10 +1615,10 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="A34">
         <v>42814075</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34">
         <v>42406507</v>
       </c>
       <c r="C34" t="s">
@@ -1638,10 +1647,10 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+      <c r="A35">
         <v>42814075</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35">
         <v>42426592</v>
       </c>
       <c r="C35" t="s">
@@ -1670,10 +1679,10 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+      <c r="A36">
         <v>42814075</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36">
         <v>42426641</v>
       </c>
       <c r="C36" t="s">
@@ -1702,10 +1711,10 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+      <c r="A37">
         <v>42814075</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37">
         <v>43110281</v>
       </c>
       <c r="C37" t="s">
@@ -1734,10 +1743,10 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+      <c r="A38">
         <v>23938356</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38">
         <v>2380983</v>
       </c>
       <c r="C38" t="s">
@@ -1766,10 +1775,10 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="A39">
         <v>23938356</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39">
         <v>2890343</v>
       </c>
       <c r="C39" t="s">
@@ -1798,10 +1807,10 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+      <c r="A40">
         <v>23938356</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40">
         <v>2890343</v>
       </c>
       <c r="C40" t="s">
@@ -1830,10 +1839,10 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+      <c r="A41">
         <v>23938356</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41">
         <v>3149860</v>
       </c>
       <c r="C41" t="s">
@@ -1862,10 +1871,10 @@
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
+      <c r="A42">
         <v>23938356</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42">
         <v>3281435</v>
       </c>
       <c r="C42" t="s">
@@ -1894,10 +1903,10 @@
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
+      <c r="A43">
         <v>23938356</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43">
         <v>26485962</v>
       </c>
       <c r="C43" t="s">
@@ -1926,10 +1935,10 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+      <c r="A44">
         <v>23938356</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44">
         <v>26485962</v>
       </c>
       <c r="C44" t="s">
@@ -1958,10 +1967,10 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
+      <c r="A45">
         <v>42459206</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45">
         <v>42459041</v>
       </c>
       <c r="C45" t="s">
@@ -1990,10 +1999,10 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+      <c r="A46">
         <v>42459206</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46">
         <v>42459041</v>
       </c>
       <c r="C46" t="s">
@@ -2022,10 +2031,10 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
+      <c r="A47">
         <v>42459206</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47">
         <v>42459148</v>
       </c>
       <c r="C47" t="s">
@@ -2054,10 +2063,10 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+      <c r="A48">
         <v>42459206</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48">
         <v>42459148</v>
       </c>
       <c r="C48" t="s">
@@ -2086,10 +2095,10 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+      <c r="A49">
         <v>42598944</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49">
         <v>42758642</v>
       </c>
       <c r="C49" t="s">
@@ -2118,10 +2127,10 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+      <c r="A50">
         <v>42598944</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50">
         <v>42814075</v>
       </c>
       <c r="C50" t="s">
@@ -2150,10 +2159,10 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+      <c r="A51">
         <v>42598944</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51">
         <v>42814075</v>
       </c>
       <c r="C51" t="s">
@@ -2182,10 +2191,10 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+      <c r="A52">
         <v>42758642</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52">
         <v>42598944</v>
       </c>
       <c r="C52" t="s">
@@ -2214,10 +2223,10 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+      <c r="A53">
         <v>42758642</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53">
         <v>42814075</v>
       </c>
       <c r="C53" t="s">
@@ -2246,10 +2255,10 @@
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+      <c r="A54">
         <v>42787717</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54">
         <v>42011766</v>
       </c>
       <c r="C54" t="s">
@@ -2278,10 +2287,10 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
+      <c r="A55">
         <v>42787717</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55">
         <v>42426641</v>
       </c>
       <c r="C55" t="s">
@@ -2310,10 +2319,10 @@
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
+      <c r="A56">
         <v>42787717</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56">
         <v>42598944</v>
       </c>
       <c r="C56" t="s">
@@ -2342,10 +2351,10 @@
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
+      <c r="A57">
         <v>42787717</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57">
         <v>42598944</v>
       </c>
       <c r="C57" t="s">
@@ -2374,10 +2383,10 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+      <c r="A58">
         <v>42787717</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58">
         <v>42758642</v>
       </c>
       <c r="C58" t="s">
@@ -2406,10 +2415,10 @@
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+      <c r="A59">
         <v>42787717</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59">
         <v>42758642</v>
       </c>
       <c r="C59" t="s">
@@ -2438,10 +2447,10 @@
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
+      <c r="A60">
         <v>42787717</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60">
         <v>42814075</v>
       </c>
       <c r="C60" t="s">
@@ -2470,10 +2479,10 @@
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
+      <c r="A61">
         <v>42787717</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61">
         <v>42814075</v>
       </c>
       <c r="C61" t="s">
@@ -2502,10 +2511,10 @@
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
+      <c r="A62">
         <v>42814075</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62">
         <v>42011766</v>
       </c>
       <c r="C62" t="s">
@@ -2534,10 +2543,10 @@
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
+      <c r="A63">
         <v>42814075</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63">
         <v>42598944</v>
       </c>
       <c r="C63" t="s">
@@ -2566,10 +2575,10 @@
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
+      <c r="A64">
         <v>42814075</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64">
         <v>42598944</v>
       </c>
       <c r="C64" t="s">
@@ -2598,10 +2607,10 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
+      <c r="A65">
         <v>42814075</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65">
         <v>42758642</v>
       </c>
       <c r="C65" t="s">
@@ -2630,10 +2639,10 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
+      <c r="A66">
         <v>42814075</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66">
         <v>42787717</v>
       </c>
       <c r="C66" t="s">
@@ -2662,10 +2671,10 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
+      <c r="A67">
         <v>42814075</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67">
         <v>42787717</v>
       </c>
       <c r="C67" t="s">
@@ -2700,328 +2709,740 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E570CF9-51C2-479D-A2DE-2E7672A52D1F}">
-  <dimension ref="A1:E27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A7D424-B2E7-4B94-B497-03DD547CEA0C}">
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2725817</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="e">
+        <f>_xlfn.XLOOKUP(A2,$F$2:$F$17,$F$2:$F$17)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F2">
+        <v>13373294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3560834</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="e">
+        <f t="shared" ref="D3:D27" si="0">_xlfn.XLOOKUP(A3,$F$2:$F$17,$F$2:$F$17)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F3" s="1">
         <v>23938356</v>
       </c>
-      <c r="B2" s="1">
-        <v>2725817</v>
-      </c>
-      <c r="C2" s="1" t="str">
-        <f>_xlfn.XLOOKUP(B2,$E$2:$E$17,$E$2:$E$17,"Not found")</f>
-        <v>Not found</v>
-      </c>
-      <c r="E2" s="3">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3728701</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F4" s="1">
+        <v>42459206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>35433398</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F5">
+        <v>42598944</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>42458992</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F6" s="1">
+        <v>42758642</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>42459099</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F7">
+        <v>42787717</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>42459241</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F8" s="1">
         <v>42814075</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>42459206</v>
-      </c>
-      <c r="B3" s="1">
-        <v>3560834</v>
-      </c>
-      <c r="C3" s="1" t="str">
-        <f t="shared" ref="C3:C27" si="0">_xlfn.XLOOKUP(B3,$E$2:$E$17,$E$2:$E$17,"Not found")</f>
-        <v>Not found</v>
-      </c>
-      <c r="E3" s="3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>42459298</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F9" s="1">
+        <v>43376946</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>42011766</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F10" s="1">
+        <v>43485077</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>42406507</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F11" s="1">
+        <v>43512432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>42426592</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F12" s="1">
+        <v>43701630</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>42426641</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F13" s="1">
+        <v>43729827</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>42787717</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>42598944</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3728701</v>
-      </c>
-      <c r="C4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E4" s="3">
-        <v>42459206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>42758642</v>
-      </c>
-      <c r="B5" s="1">
-        <v>35433398</v>
-      </c>
-      <c r="C5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E5" s="3">
-        <v>42758642</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>42787717</v>
-      </c>
-      <c r="B6" s="1">
-        <v>42458992</v>
-      </c>
-      <c r="C6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E6" s="3">
-        <v>42598944</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>42814075</v>
-      </c>
-      <c r="B7" s="1">
-        <v>42459099</v>
-      </c>
-      <c r="C7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E7" s="3">
-        <v>43376946</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="1">
-        <v>42459241</v>
-      </c>
-      <c r="C8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E8" s="3">
-        <v>43485077</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="1">
-        <v>42459298</v>
-      </c>
-      <c r="C9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E9" s="3">
-        <v>43512432</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="1">
-        <v>42011766</v>
-      </c>
-      <c r="C10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E10" s="3">
-        <v>43701630</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="1">
-        <v>42406507</v>
-      </c>
-      <c r="C11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E11" s="3">
-        <v>43729827</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="1">
-        <v>42426592</v>
-      </c>
-      <c r="C12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E12" s="3">
-        <v>13373294</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="1">
-        <v>42426641</v>
-      </c>
-      <c r="C13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E13" s="3">
-        <v>23938356</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="4">
-        <v>42787717</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14">
         <f t="shared" si="0"/>
         <v>42787717</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="1">
+        <v>43740668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>43110281</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="F15" s="1">
         <v>43756635</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="1">
-        <v>43110281</v>
-      </c>
-      <c r="C15" s="1" t="str">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>42705635</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="e">
         <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E15" s="3">
-        <v>43740668</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="1">
-        <v>42705635</v>
-      </c>
-      <c r="C16" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="F16" s="1">
+        <v>43783789</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>42731028</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="e">
         <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E16" s="3">
-        <v>43783789</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="1">
-        <v>42731028</v>
-      </c>
-      <c r="C17" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="F17" s="1">
+        <v>43811059</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2380983</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="e">
         <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-      <c r="E17" s="3">
-        <v>43811059</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="1">
-        <v>2380983</v>
-      </c>
-      <c r="C18" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2890343</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="e">
         <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="1">
-        <v>2890343</v>
-      </c>
-      <c r="C19" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>3149860</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="e">
         <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="1">
-        <v>3149860</v>
-      </c>
-      <c r="C20" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>3281435</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="e">
         <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="1">
-        <v>3281435</v>
-      </c>
-      <c r="C21" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>26485962</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="e">
         <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="1">
-        <v>26485962</v>
-      </c>
-      <c r="C22" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>42459041</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="e">
         <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="1">
-        <v>42459041</v>
-      </c>
-      <c r="C23" s="1" t="str">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>42459148</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" t="e">
         <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="1">
-        <v>42459148</v>
-      </c>
-      <c r="C24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Not found</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>42758642</v>
       </c>
-      <c r="C25" s="1">
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25">
         <f t="shared" si="0"/>
         <v>42758642</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="4">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>42814075</v>
       </c>
-      <c r="C26" s="1">
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26">
         <f t="shared" si="0"/>
         <v>42814075</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="4">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>42598944</v>
       </c>
-      <c r="C27" s="1">
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27">
         <f t="shared" si="0"/>
         <v>42598944</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016BDD55-BEB4-46A1-BB59-4A1113469436}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>2725817</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>3560834</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3728701</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>35433398</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>42458992</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>42459099</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>42459241</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>42459298</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>42011766</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>42406507</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>42426592</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>42426641</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>43110281</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>42705635</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>42731028</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>2380983</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>2890343</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>3149860</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>3281435</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>26485962</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>42459041</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>42459148</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>